--- a/outputs/tables/tabla_04_indicadores_riesgo.xlsx
+++ b/outputs/tables/tabla_04_indicadores_riesgo.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="indicadores_riesgo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,12 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>valor_%</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>interpretacion</t>
+          <t>valor_pct</t>
         </is>
       </c>
     </row>
@@ -440,72 +435,67 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15.02989455538528</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Variabilidad esperada del COP/CAD en un ano tipico</t>
-        </is>
+        <v>13.94037267306967</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VaR diario (95%)</t>
+          <t>VaR 1d 95%</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-1.455239717146715</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Perdida maxima esperada en 1 dia, con 95% de confianza</t>
-        </is>
+        <v>-1.304242917754134</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VaR 30 dias (95%)</t>
+          <t>VaR 1d 99%</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-7.970676196586934</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Perdida maxima esperada en 30 dias, con 95% de confianza</t>
-        </is>
+        <v>-2.321629973801954</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VaR 60 dias (95%)</t>
+          <t>Expected Shortfall 95%</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-11.27223837849764</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Perdida maxima esperada en 60 dias, con 95% de confianza</t>
-        </is>
+        <v>-1.92614014196939</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VaR 90 dias (95%)</t>
+          <t>VaR 30d 95% (empirico)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-13.80561614316843</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Perdida maxima esperada en 90 dias, con 95% de confianza</t>
-        </is>
+        <v>-6.653590974549179</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>VaR 60d 95% (empirico)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>-9.498385780837847</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>VaR 90d 95% (empirico)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-11.63970946329207</v>
       </c>
     </row>
   </sheetData>
